--- a/static/data/Experience.xlsx
+++ b/static/data/Experience.xlsx
@@ -34,13 +34,13 @@
     <t>duration</t>
   </si>
   <si>
-    <t>Software Engineer (II)</t>
-  </si>
-  <si>
-    <t>Feb 2026 - Present · Rajshahi, Bangladesh · Hybrid</t>
-  </si>
-  <si>
-    <t>Software Engineer I (Python)</t>
+    <t>Software Engineer II</t>
+  </si>
+  <si>
+    <t>Feb 2026 - Present</t>
+  </si>
+  <si>
+    <t>Software Engineer I</t>
   </si>
   <si>
     <t>December 2023 - Jan 2026</t>
@@ -531,7 +531,10 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="2" width="13.571428571428571" customWidth="1"/>
+    <col min="3" max="3" width="37.142857142857146" customWidth="1"/>
+    <col min="4" max="4" width="43.57142857142857" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
